--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.1_Regulatory_Inventory_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.1_Regulatory_Inventory_20260208.xlsx
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="3">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="4">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="5">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="6">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="7">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="8">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>NIST Cybersecurity Framework v2.0</t>
+          <t>NIST Cybersecurity Framework (CSF) 2.0 v2.0</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
     <row r="9">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>46061.49234961349</v>
+        <v>46061.51766977082</v>
       </c>
     </row>
   </sheetData>
